--- a/input/Signup.xlsx
+++ b/input/Signup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C10CA3-7708-48D0-B45E-C254EFC455C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4B609E-7052-422D-AB10-AAA91E45927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
+    <workbookView xWindow="28605" yWindow="1335" windowWidth="15375" windowHeight="7785" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
   <sheets>
     <sheet name="signup" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -50,26 +50,35 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>08-07-1999</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
-    <t xml:space="preserve">Mobile Number </t>
+    <t>8526668420</t>
+  </si>
+  <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>8/10/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF5C92FF"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,10 +101,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,14 +443,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F873A05F-98AA-4B8C-BC99-F5F8F22A7373}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,25 +460,26 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D2">
-        <v>8526668420</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>